--- a/jyd_plain_json_probe/apps/processor/frontend/new/project-script-template.xlsx
+++ b/jyd_plain_json_probe/apps/processor/frontend/new/project-script-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脚本导入模板" sheetId="1" r:id="Rf30c1d97b50548d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脚本导入模板" sheetId="1" r:id="R0093838ac90a4c55"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -27,8 +27,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -40,8 +46,13 @@
         <x:fgColor rgb="FF4F46E5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4F46E5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -96,12 +107,17 @@
       <x:top style="thin">
         <x:color rgb="FFCBD5E1"/>
       </x:top>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E1F2"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -137,6 +153,25 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -343,14 +378,22 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
+    <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="9" t="str">
         <x:v>任务ID</x:v>
       </x:c>
       <x:c r="B1" s="10" t="str">
         <x:v>脚本内容</x:v>
+      </x:c>
+      <x:c r="C1" s="17" t="str">
+        <x:v>文章类型</x:v>
+      </x:c>
+      <x:c r="D1" s="17" t="str">
+        <x:v>分配账号</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
@@ -360,6 +403,12 @@
       <x:c r="B2" s="12" t="str">
         <x:v>请在这里填写第一条需要生成视频的完整脚本文案。</x:v>
       </x:c>
+      <x:c r="C2" s="22" t="str">
+        <x:v>干货类</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="11" t="str">
@@ -368,6 +417,12 @@
       <x:c r="B3" s="12" t="str">
         <x:v>请在这里填写第二条脚本文案，每一行对应一个视频任务。</x:v>
       </x:c>
+      <x:c r="C3" s="22" t="str">
+        <x:v>鸡汤文</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="13" t="str">
@@ -375,6 +430,12 @@
       </x:c>
       <x:c r="B4" s="14" t="str">
         <x:v>任务ID用于编号，必须唯一；脚本内容不能为空。</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>带人设介绍的干货类</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/jyd_plain_json_probe/apps/processor/frontend/new/project-script-template.xlsx
+++ b/jyd_plain_json_probe/apps/processor/frontend/new/project-script-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脚本导入模板" sheetId="1" r:id="R0093838ac90a4c55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脚本导入模板" sheetId="1" r:id="Re70ee4e28eb8491c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -403,40 +403,20 @@
       <x:c r="B2" s="12" t="str">
         <x:v>请在这里填写第一条需要生成视频的完整脚本文案。</x:v>
       </x:c>
-      <x:c r="C2" s="22" t="str">
-        <x:v>干货类</x:v>
-      </x:c>
-      <x:c r="D2" s="20" t="str">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C2" s="22"/>
+      <x:c r="D2" s="20"/>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
-      <x:c r="A3" s="11" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="str">
-        <x:v>请在这里填写第二条脚本文案，每一行对应一个视频任务。</x:v>
-      </x:c>
-      <x:c r="C3" s="22" t="str">
-        <x:v>鸡汤文</x:v>
-      </x:c>
-      <x:c r="D3" s="20" t="str">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="A3" s="11"/>
+      <x:c r="B3" s="12"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="20"/>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
-      <x:c r="A4" s="13" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="14" t="str">
-        <x:v>任务ID用于编号，必须唯一；脚本内容不能为空。</x:v>
-      </x:c>
-      <x:c r="C4" s="23" t="str">
-        <x:v>带人设介绍的干货类</x:v>
-      </x:c>
-      <x:c r="D4" s="21" t="str">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A4" s="13"/>
+      <x:c r="B4" s="14"/>
+      <x:c r="C4" s="23"/>
+      <x:c r="D4" s="21"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
